--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10512"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-master/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D26860-A1BF-2D4F-8C24-A8428E443286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7A7345-52ED-F54D-9AC0-DC17D66615E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="760" windowWidth="20600" windowHeight="17500" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -52,13 +52,13 @@
     <sheet name="SDDCs" sheetId="58" r:id="rId37"/>
     <sheet name="SDDCs-Network" sheetId="59" r:id="rId38"/>
     <sheet name="Buckets" sheetId="54" r:id="rId39"/>
-    <sheet name="drop_down_rule_set" sheetId="44" state="hidden" r:id="rId40"/>
-    <sheet name="Database_Dropdown" sheetId="47" state="hidden" r:id="rId41"/>
-    <sheet name="LB Rule Set Dropdown" sheetId="48" state="hidden" r:id="rId42"/>
-    <sheet name="drop_down_rule_comp" sheetId="49" state="hidden" r:id="rId43"/>
+    <sheet name="KMS" sheetId="62" r:id="rId40"/>
+    <sheet name="drop_down_rule_set" sheetId="44" state="hidden" r:id="rId41"/>
+    <sheet name="Database_Dropdown" sheetId="47" state="hidden" r:id="rId42"/>
+    <sheet name="LB Rule Set Dropdown" sheetId="48" state="hidden" r:id="rId43"/>
+    <sheet name="drop_down_rule_comp" sheetId="49" state="hidden" r:id="rId44"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId44"/>
     <externalReference r:id="rId45"/>
     <externalReference r:id="rId46"/>
     <externalReference r:id="rId47"/>
@@ -69,19 +69,21 @@
     <externalReference r:id="rId52"/>
     <externalReference r:id="rId53"/>
     <externalReference r:id="rId54"/>
+    <externalReference r:id="rId55"/>
   </externalReferences>
   <definedNames>
     <definedName name="Action_Values" localSheetId="28">#REF!</definedName>
     <definedName name="Allowed_Methods" localSheetId="28">#REF!</definedName>
     <definedName name="Attribute_Names" localSheetId="28">#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="38">[1]Database_Dropdown!#REF!</definedName>
-    <definedName name="bm_shapes_drop" localSheetId="40">Database_Dropdown!#REF!</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="41">Database_Dropdown!#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="19">[1]Database_Dropdown!#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="18">[1]Database_Dropdown!#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="14">[2]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="bm_shapes_drop" localSheetId="10">[3]Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="bm_shapes_drop" localSheetId="42">[4]Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="bm_shapes_drop" localSheetId="39">[5]Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="43">[4]Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="40">[5]Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="39">[1]Database_Dropdown!#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="4">#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="31">[6]Database_Dropdown!#REF!</definedName>
     <definedName name="bm_shapes_drop" localSheetId="30">[6]Database_Dropdown!#REF!</definedName>
@@ -91,14 +93,15 @@
     <definedName name="bm_shapes_drop" localSheetId="3">#REF!</definedName>
     <definedName name="bm_shapes_drop">#REF!</definedName>
     <definedName name="char_set" localSheetId="38">[1]Database_Dropdown!$H$2:$H$108</definedName>
-    <definedName name="char_set" localSheetId="40">Database_Dropdown!$H$2:$H$108</definedName>
+    <definedName name="char_set" localSheetId="41">Database_Dropdown!$H$2:$H$108</definedName>
     <definedName name="char_set" localSheetId="19">[1]Database_Dropdown!$H$2:$H$108</definedName>
     <definedName name="char_set" localSheetId="18">[1]Database_Dropdown!$H$2:$H$108</definedName>
     <definedName name="char_set" localSheetId="14">[2]Database_Dropdown!$I$2:$I$108</definedName>
     <definedName name="char_set" localSheetId="10">[3]Database_Dropdown!$I$2:$I$108</definedName>
-    <definedName name="char_set" localSheetId="42">[4]Database_Dropdown!$I$2:$I$108</definedName>
-    <definedName name="char_set" localSheetId="39">[5]Database_Dropdown!$I$2:$I$108</definedName>
-    <definedName name="char_set" localSheetId="41">#REF!</definedName>
+    <definedName name="char_set" localSheetId="43">[4]Database_Dropdown!$I$2:$I$108</definedName>
+    <definedName name="char_set" localSheetId="40">[5]Database_Dropdown!$I$2:$I$108</definedName>
+    <definedName name="char_set" localSheetId="39">[1]Database_Dropdown!$H$2:$H$108</definedName>
+    <definedName name="char_set" localSheetId="42">#REF!</definedName>
     <definedName name="char_set" localSheetId="4">#REF!</definedName>
     <definedName name="char_set" localSheetId="31">[6]Database_Dropdown!$H$2:$H$108</definedName>
     <definedName name="char_set" localSheetId="30">[6]Database_Dropdown!$H$2:$H$108</definedName>
@@ -111,13 +114,14 @@
     <definedName name="D3D1000" localSheetId="3">'[8]DBSystems-VM-BM'!#REF!</definedName>
     <definedName name="D3D1000">'DBSystems-VM-BM'!#REF!</definedName>
     <definedName name="db_sersion_drop" localSheetId="38">[1]Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="db_sersion_drop" localSheetId="40">Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="41">Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="19">[1]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="18">[1]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="14">[2]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="10">[3]Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="db_sersion_drop" localSheetId="42">[4]Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="db_sersion_drop" localSheetId="39">[5]Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="43">[4]Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="40">[5]Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="39">[1]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="4">#REF!</definedName>
     <definedName name="db_sersion_drop" localSheetId="31">[6]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop" localSheetId="30">[6]Database_Dropdown!$C$2:$C$14</definedName>
@@ -127,13 +131,14 @@
     <definedName name="db_sersion_drop" localSheetId="3">#REF!</definedName>
     <definedName name="db_sersion_drop">#REF!</definedName>
     <definedName name="exa_shapes_drop" localSheetId="38">[1]Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="40">Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="41">Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="19">[1]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="18">[1]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="14">[2]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="10">[3]Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="42">[4]Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="39">[5]Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="43">[4]Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="40">[5]Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="39">[1]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="4">#REF!</definedName>
     <definedName name="exa_shapes_drop" localSheetId="31">[6]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="30">[6]Database_Dropdown!$E$2:$E$11</definedName>
@@ -142,12 +147,12 @@
     <definedName name="exa_shapes_drop" localSheetId="37">[1]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop" localSheetId="3">#REF!</definedName>
     <definedName name="exa_shapes_drop">#REF!</definedName>
-    <definedName name="Header_Size" localSheetId="40">'[9]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
+    <definedName name="Header_Size" localSheetId="41">'[9]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size" localSheetId="14">'[2]Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size" localSheetId="10">'[3]Rule Set Dropdown'!$F$2:$F$6</definedName>
-    <definedName name="Header_Size" localSheetId="42">'[4]Rule Set Dropdown'!$F$2:$F$6</definedName>
-    <definedName name="Header_Size" localSheetId="39">#REF!</definedName>
-    <definedName name="Header_Size" localSheetId="41">'LB Rule Set Dropdown'!$F$2:$F$6</definedName>
+    <definedName name="Header_Size" localSheetId="43">'[4]Rule Set Dropdown'!$F$2:$F$6</definedName>
+    <definedName name="Header_Size" localSheetId="40">#REF!</definedName>
+    <definedName name="Header_Size" localSheetId="42">'LB Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size" localSheetId="4">'[8]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size" localSheetId="31">'[6]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size" localSheetId="30">'[6]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
@@ -155,13 +160,14 @@
     <definedName name="Header_Size" localSheetId="3">'[8]LB Rule Set Dropdown'!$F$2:$F$6</definedName>
     <definedName name="Header_Size">#REF!</definedName>
     <definedName name="license_type_drop" localSheetId="38">[1]Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="license_type_drop" localSheetId="40">Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="license_type_drop" localSheetId="41">Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="license_type_drop" localSheetId="19">[1]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="license_type_drop" localSheetId="18">[1]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="license_type_drop" localSheetId="14">[2]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="license_type_drop" localSheetId="10">[3]Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="license_type_drop" localSheetId="42">[4]Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="license_type_drop" localSheetId="39">[5]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="license_type_drop" localSheetId="43">[4]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="license_type_drop" localSheetId="40">[5]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="license_type_drop" localSheetId="39">[1]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="license_type_drop" localSheetId="4">#REF!</definedName>
     <definedName name="license_type_drop" localSheetId="31">[6]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="license_type_drop" localSheetId="30">[6]Database_Dropdown!$F$2:$F$3</definedName>
@@ -173,14 +179,15 @@
     <definedName name="Match_Style" localSheetId="29">#REF!</definedName>
     <definedName name="Match_Style" localSheetId="28">#REF!</definedName>
     <definedName name="nchar_set" localSheetId="38">[1]Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="nchar_set" localSheetId="40">Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="nchar_set" localSheetId="41">Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="nchar_set" localSheetId="19">[1]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="nchar_set" localSheetId="18">[1]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="nchar_set" localSheetId="14">[2]Database_Dropdown!$H$2:$H$3</definedName>
     <definedName name="nchar_set" localSheetId="10">[3]Database_Dropdown!$H$2:$H$3</definedName>
-    <definedName name="nchar_set" localSheetId="42">[4]Database_Dropdown!$H$2:$H$3</definedName>
-    <definedName name="nchar_set" localSheetId="39">[5]Database_Dropdown!$H$2:$H$3</definedName>
-    <definedName name="nchar_set" localSheetId="41">#REF!</definedName>
+    <definedName name="nchar_set" localSheetId="43">[4]Database_Dropdown!$H$2:$H$3</definedName>
+    <definedName name="nchar_set" localSheetId="40">[5]Database_Dropdown!$H$2:$H$3</definedName>
+    <definedName name="nchar_set" localSheetId="39">[1]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="nchar_set" localSheetId="42">#REF!</definedName>
     <definedName name="nchar_set" localSheetId="4">#REF!</definedName>
     <definedName name="nchar_set" localSheetId="31">[6]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="nchar_set" localSheetId="30">[6]Database_Dropdown!$G$2:$G$3</definedName>
@@ -189,12 +196,12 @@
     <definedName name="nchar_set" localSheetId="37">[1]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="nchar_set" localSheetId="3">#REF!</definedName>
     <definedName name="nchar_set">#REF!</definedName>
-    <definedName name="Response_Code" localSheetId="40">'[9]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Response_Code" localSheetId="41">'[9]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code" localSheetId="14">'[2]Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code" localSheetId="10">'[3]Rule Set Dropdown'!$E$2:$E$7</definedName>
-    <definedName name="Response_Code" localSheetId="42">'[4]Rule Set Dropdown'!$E$2:$E$7</definedName>
-    <definedName name="Response_Code" localSheetId="39">#REF!</definedName>
-    <definedName name="Response_Code" localSheetId="41">'LB Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Response_Code" localSheetId="43">'[4]Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Response_Code" localSheetId="40">#REF!</definedName>
+    <definedName name="Response_Code" localSheetId="42">'LB Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code" localSheetId="4">'[8]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code" localSheetId="31">'[6]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code" localSheetId="30">'[6]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
@@ -202,15 +209,16 @@
     <definedName name="Response_Code" localSheetId="3">'[8]LB Rule Set Dropdown'!$E$2:$E$7</definedName>
     <definedName name="Response_Code">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="38">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="40">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="41">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="33">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="19">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="18">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="14">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="10">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="42">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="43">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="40">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="35">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="39">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="35">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="4">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="31">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="30">#REF!</definedName>
@@ -221,13 +229,14 @@
     <definedName name="Shape_Option">#REF!</definedName>
     <definedName name="Shape_Option_DB">[11]Database!$B$10:$J$10</definedName>
     <definedName name="software_drop" localSheetId="38">[1]Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="software_drop" localSheetId="40">Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="41">Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="19">[1]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="18">[1]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="14">[2]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="10">[3]Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="software_drop" localSheetId="42">[4]Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="software_drop" localSheetId="39">[5]Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="43">[4]Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="40">[5]Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="39">[1]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="4">#REF!</definedName>
     <definedName name="software_drop" localSheetId="31">[6]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="30">[6]Database_Dropdown!$B$2:$B$5</definedName>
@@ -236,18 +245,19 @@
     <definedName name="software_drop" localSheetId="37">[1]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop" localSheetId="3">#REF!</definedName>
     <definedName name="software_drop">#REF!</definedName>
-    <definedName name="VM_Shapes" localSheetId="40">Database_Dropdown!$A$2:$A$12</definedName>
+    <definedName name="VM_Shapes" localSheetId="41">Database_Dropdown!$A$2:$A$12</definedName>
     <definedName name="VM_Shapes" localSheetId="14">#REF!</definedName>
     <definedName name="VM_Shapes" localSheetId="10">#REF!</definedName>
     <definedName name="VM_Shapes">'DBSystems-VM-BM'!$AB$390:$AB$400</definedName>
     <definedName name="VM_shapes_drop" localSheetId="38">[1]Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="40">Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="41">Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="19">[1]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="18">[1]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="14">[2]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="10">[3]Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="42">[4]Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="39">[5]Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="43">[4]Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="40">[5]Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="39">[1]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="4">#REF!</definedName>
     <definedName name="VM_shapes_drop" localSheetId="31">[6]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop" localSheetId="30">[6]Database_Dropdown!$A$2:$A$7</definedName>
@@ -257,13 +267,14 @@
     <definedName name="VM_shapes_drop" localSheetId="3">#REF!</definedName>
     <definedName name="VM_shapes_drop">#REF!</definedName>
     <definedName name="workload_drop" localSheetId="38">[1]Database_Dropdown!$D$2:$D$3</definedName>
-    <definedName name="workload_drop" localSheetId="40">Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="41">Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="19">[1]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="18">[1]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="14">[2]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="10">[3]Database_Dropdown!$D$2:$D$3</definedName>
-    <definedName name="workload_drop" localSheetId="42">[4]Database_Dropdown!$D$2:$D$3</definedName>
-    <definedName name="workload_drop" localSheetId="39">[5]Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="43">[4]Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="40">[5]Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="39">[1]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="4">#REF!</definedName>
     <definedName name="workload_drop" localSheetId="31">[6]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop" localSheetId="30">[6]Database_Dropdown!$D$2:$D$3</definedName>
@@ -376,7 +387,7 @@
     <author>Suruchi</author>
   </authors>
   <commentList>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{F0D32B47-E310-7246-8369-2EDE96F2D473}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{DFA3381A-B6E3-8642-9D9B-F59DB2F382DA}">
       <text>
         <r>
           <rPr>
@@ -386,52 +397,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Enter OCID of the source snapshot to create clone FSS
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>or leave empty to create empty FSS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{0B1EC56D-B6AF-D24E-B30D-FBAFC2FE71EC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Enter OCID of the snapshot policy to be attached to the FSS.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
         </r>
       </text>
     </comment>
@@ -746,7 +712,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="757">
   <si>
     <t>Region</t>
   </si>
@@ -1003,40 +969,7 @@
     <t>paravirtualized</t>
   </si>
   <si>
-    <t>MountTarget Name</t>
-  </si>
-  <si>
-    <t>MountTarget SubnetName</t>
-  </si>
-  <si>
-    <t>MountTarget IP</t>
-  </si>
-  <si>
-    <t>MountTarget Hostname</t>
-  </si>
-  <si>
-    <t>FSS Name</t>
-  </si>
-  <si>
     <t>Path</t>
-  </si>
-  <si>
-    <t>Source CIDR</t>
-  </si>
-  <si>
-    <t>Access (READ_ONLY|READ_WRITE)</t>
-  </si>
-  <si>
-    <t>GID</t>
-  </si>
-  <si>
-    <t>UID</t>
-  </si>
-  <si>
-    <t>IDSquash (NONE|ALL|ROOT)</t>
-  </si>
-  <si>
-    <t>Require PS Port (true|false)</t>
   </si>
   <si>
     <t>READ_WRITE</t>
@@ -2152,45 +2085,6 @@
   </si>
   <si>
     <t>Source Details</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Note:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Default value for columns if left blank: sourceCIDR- 0.0.0.0/0, Access- READ_ONLY, GID- 65534, UID- 65534, IDSquash- NONE and Require PS Port- false.
-Mount target IP will take default values from OCI if left blank.
-Resources will be created based on 'MountTarget Name' and 'FSS Name' columns.
-Below sample data shows example of  multiple FSS(FSS1 and FSS2) using single MT(MT1) , 1 FSS(FSS3) using multiple MTs(MT2 and MT3) and also 1 FSS(FSS4) using 1 MT(MT4).</t>
-    </r>
   </si>
   <si>
     <t>Exadata.Half3.200</t>
@@ -8733,55 +8627,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2024.3.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- VCNs, OKE, OCVS, Block Volumes, FSS, Quota Policies, Budgets, Key/Vaults</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
 "Region" -</t>
     </r>
@@ -9348,6 +9193,884 @@
     </r>
   </si>
   <si>
+    <t>Autotune Type</t>
+  </si>
+  <si>
+    <t>Max VPUS Per GB</t>
+  </si>
+  <si>
+    <t>Block Volume Replica (Region::AD::Name)</t>
+  </si>
+  <si>
+    <t>Cross Region Replication</t>
+  </si>
+  <si>
+    <t>Backend HealthCheck Protocol(HTTP|HTTPS|TCP|UDP|DNS)</t>
+  </si>
+  <si>
+    <t>Domain Name</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+"SDDC name" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SDDC Name should match exactly the same as in SDDCs sheet.  For each SDDC Cluster in SDDCs sheet, there should be one row in this sheet defining the network for SDDC. 
+&lt;SDDC Name&gt;::&lt;Cluster Name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2024.3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ VCNs, OKE, OCVS, Block Volumes, FSS, Quota Policies, Budgets, KMS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Vault Display Name(mandatory)"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Should Not be more than 100 characters and should contain only Alpha-Numeric Characters, underscores, hyphens.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Vault Type(mandatory)"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Valid values are</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"virtual_private</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Replica Region(optional)"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Valid only for vault type: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"virtual_private"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Can't be same as the primary vault region.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Key details can be left empty if no keys have to be created in the specified vault.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+If a key/keys have to be created, enter below </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mandatory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fields:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Key Compartment Name" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-  can be same as the Vault compartment or a different compartment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Key Display Name"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Should Not be more than 100 characters and should contain only Alpha-Numeric Characters, underscores, hyphens
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Protection Mode" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Valid values are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"HSM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"SOFTWARE".</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Algorithm" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Valid values are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"AES", "RSA", "ECDSA". </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Length in bits" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Valid values for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"AES"  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">      -  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>128, 192, 256</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                                                           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"RSA" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">      - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2048, 3072, 4096</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                                                                          "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECDSA"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   -  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>256, 384, 521</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Below are the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>optional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> parameters:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Curve Id" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Can only be specified for ECDSA keys. Supported values are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"NIST_P256", "NIST_P384", "NIST_P521" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">depending on the length provided for ecdsa key.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Auto Rotation" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Only supported for vault type:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "virtual_private"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to enable auto rotation, else leave empty</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Rotation Interval in days" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Only valid for virtual private vaults with Auto rotation enabled. Value should be between </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>60-365.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Vault/Key Defined Tags" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                             </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">Example: Operations.CostCenter=01;Users.Name=user01" 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>o create multiple keys in the same vault, specify the key details as shown in below sample data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vault Compartment Name</t>
+  </si>
+  <si>
+    <t>Vault Display Name</t>
+  </si>
+  <si>
+    <t>Vault type</t>
+  </si>
+  <si>
+    <t>Replica Region</t>
+  </si>
+  <si>
+    <t>Vault Defined Tags</t>
+  </si>
+  <si>
+    <t>Key Compartment Name</t>
+  </si>
+  <si>
+    <t>Key Display Name</t>
+  </si>
+  <si>
+    <t>Protection mode</t>
+  </si>
+  <si>
+    <t>Algorithm</t>
+  </si>
+  <si>
+    <t>Length in bits</t>
+  </si>
+  <si>
+    <t>Curve Id</t>
+  </si>
+  <si>
+    <t>Auto rotation</t>
+  </si>
+  <si>
+    <t>Rotation interval in days</t>
+  </si>
+  <si>
+    <t>Key Defined Tags</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
 "Attached To Instance"  - </t>
@@ -9404,7 +10127,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Leave it empty for new volume or enter OCID of volume|volume backup|volume replica as source for new volume.</t>
+      <t xml:space="preserve">Leave it empty for new volume or Specify if the block volume is to be created from volume or volumeBackup or blockVolumeReplica.
+                                    Format - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>volume::&lt;variable containing volume ocid under blockvolume_source_ocids&gt; (or)  volumeBackup::&lt;variable containing volume backup ocid under blockvolume_source_ocids&gt;  (or)  blockVolumeReplica::&lt;variable containing volume replica  ocid under blockvolume_source_ocid&gt;</t>
     </r>
     <r>
       <rPr>
@@ -9592,211 +10325,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-  </si>
-  <si>
-    <t>Autotune Type</t>
-  </si>
-  <si>
-    <t>Max VPUS Per GB</t>
-  </si>
-  <si>
-    <t>Block Volume Replica (Region::AD::Name)</t>
-  </si>
-  <si>
-    <t>Cross Region Replication</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
-Freeform and Defined Tags - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter subnet name as : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>vcn-name&gt;_&lt;subnet-name&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Replication Information: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Format - TargetFSSOCID::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Source Snapshot</t>
-  </si>
-  <si>
-    <t>Snapshot Policy</t>
-  </si>
-  <si>
-    <t>Replication Information</t>
-  </si>
-  <si>
-    <t>Is Anonymous Access Allowed</t>
-  </si>
-  <si>
-    <t>Allowed Auth</t>
-  </si>
-  <si>
-    <t>Backend HealthCheck Protocol(HTTP|HTTPS|TCP|UDP|DNS)</t>
-  </si>
-  <si>
-    <t>Domain Name</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-"SDDC name" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SDDC Name should match exactly the same as in SDDCs sheet.  For each SDDC Cluster in SDDCs sheet, there should be one row in this sheet defining the network for SDDC. 
-&lt;SDDC Name&gt;::&lt;Cluster Name&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
     </r>
   </si>
 </sst>
@@ -9804,7 +10332,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9948,15 +10476,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -10401,11 +10920,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -10503,8 +11022,8 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="25" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10513,16 +11032,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10531,7 +11050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10572,7 +11091,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -10592,7 +11111,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10601,8 +11120,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="38" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="38" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -10647,15 +11205,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -10665,47 +11214,22 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="39" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="39" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15911,7 +16435,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -15941,22 +16465,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>744</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="83" t="s">
-        <v>648</v>
-      </c>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="85"/>
+      <c r="A1" s="100" t="s">
+        <v>731</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="100" t="s">
+        <v>636</v>
+      </c>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="102"/>
     </row>
     <row r="2" spans="1:12" s="34" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
@@ -15969,7 +16493,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -15993,7 +16517,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -16030,19 +16554,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>528</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="89" t="s">
-        <v>706</v>
-      </c>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
+      <c r="A1" s="97" t="s">
+        <v>516</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="106" t="s">
+        <v>694</v>
+      </c>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -16052,25 +16576,25 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="G2" s="67" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -16100,10 +16624,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="34" customFormat="1" ht="94" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>512</v>
-      </c>
-      <c r="B1" s="88"/>
+      <c r="A1" s="97" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -16115,19 +16639,19 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B3" s="29"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B4" s="29"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B5" s="29"/>
     </row>
@@ -16162,16 +16686,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
     </row>
     <row r="2" spans="1:8" s="34" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -16196,7 +16720,7 @@
         <v>26</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -16241,30 +16765,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="192.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>649</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="90" t="s">
-        <v>650</v>
-      </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
+      <c r="A1" s="100" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="107" t="s">
+        <v>638</v>
+      </c>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
     </row>
     <row r="2" spans="1:20" s="34" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -16277,10 +16801,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>11</v>
@@ -16325,7 +16849,7 @@
         <v>18</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
@@ -21173,18 +21697,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>652</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>640</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
     </row>
     <row r="2" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -21194,28 +21718,28 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>46</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="K2" s="41"/>
     </row>
@@ -21250,17 +21774,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>653</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -21288,7 +21812,7 @@
         <v>47</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -21322,25 +21846,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>654</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>642</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -21392,7 +21916,7 @@
         <v>47</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -21430,28 +21954,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="125.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>655</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>643</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
@@ -21509,10 +22033,10 @@
         <v>47</v>
       </c>
       <c r="S2" s="40" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="T2" s="40" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -21547,17 +22071,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>656</v>
-      </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
+      <c r="A1" s="97" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
@@ -21567,25 +22091,25 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="74" customFormat="1" x14ac:dyDescent="0.2">
@@ -21872,13 +22396,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>644</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -21894,7 +22418,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -21931,19 +22455,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
-        <v>663</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
+      <c r="A1" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -21956,28 +22480,28 @@
         <v>10</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="74" customFormat="1" x14ac:dyDescent="0.2">
@@ -22047,15 +22571,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>670</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>658</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="1:7" s="34" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -22065,7 +22589,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>66</v>
@@ -22077,7 +22601,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -22123,33 +22647,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="226" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
-        <v>721</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="83" t="s">
-        <v>712</v>
-      </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="85"/>
+      <c r="A1" s="111" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="100" t="s">
+        <v>700</v>
+      </c>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="102"/>
     </row>
     <row r="2" spans="1:23" s="34" customFormat="1" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -22162,7 +22686,7 @@
         <v>66</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>68</v>
@@ -22177,25 +22701,25 @@
         <v>71</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="J2" s="26" t="s">
         <v>67</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="P2" s="26" t="s">
         <v>72</v>
@@ -22204,7 +22728,7 @@
         <v>73</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="S2" s="26" t="s">
         <v>74</v>
@@ -22213,10 +22737,10 @@
         <v>75</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -22252,27 +22776,27 @@
     <col min="12" max="12" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="184" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="85"/>
+    <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="100" t="s">
+        <v>756</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="102"/>
     </row>
     <row r="2" spans="1:18" s="34" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -22285,7 +22809,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>81</v>
@@ -22300,34 +22824,34 @@
         <v>83</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>73</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -22335,7 +22859,7 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" sqref="A3:XFD1048576 O1:XFD2 A1:J2 L1:M2 N1" xr:uid="{A635500E-EE4D-A744-A092-30D24AA5305C}"/>
+    <dataValidation allowBlank="1" sqref="A3:XFD1048576 L1:M2 O2:XFD2 A1:J2 N1:XFD1" xr:uid="{A635500E-EE4D-A744-A092-30D24AA5305C}"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{4D44F0E6-8DA8-6643-94F3-60D6E9B7E273}"/>
     <dataValidation type="list" sqref="K1:K2" xr:uid="{134129DE-CDBC-BC4A-9391-BD75D6E000B4}">
       <formula1>"BOTH,PERFORMANCE_BASED,DETACHED_VOLUME"</formula1>
@@ -22352,7 +22876,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -22373,110 +22897,94 @@
     <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>750</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="99"/>
-    </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+    <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="100" t="s">
+        <v>756</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="102"/>
+    </row>
+    <row r="2" spans="1:18" s="34" customFormat="1" ht="96" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>661</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>87</v>
-      </c>
       <c r="G2" s="27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>89</v>
+        <v>504</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>751</v>
+        <v>263</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>90</v>
+        <v>734</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>91</v>
+        <v>735</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>92</v>
+        <v>503</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>94</v>
+        <v>378</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="S2" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="T2" s="27" t="s">
-        <v>754</v>
-      </c>
-      <c r="U2" s="27" t="s">
-        <v>755</v>
-      </c>
-      <c r="V2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="M1:V1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="A3:XFD1048576 B2:L2 A1:A2 M1:S2 U1:XFD2" xr:uid="{02462EBB-6C3D-AD4C-90E1-0F01761ACD92}"/>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="T1:T2" xr:uid="{B87E6E22-C5FB-0747-A06C-F7AA46E8316A}"/>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" sqref="A3:XFD1048576 A1:J2 L1:M2 O1:XFD2 N1" xr:uid="{02462EBB-6C3D-AD4C-90E1-0F01761ACD92}"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{44F44AA6-F9A2-F043-9A7C-E9C593C12245}"/>
+    <dataValidation type="list" sqref="K1:K2" xr:uid="{296BAB61-C7D2-7746-8608-28C808FD0978}">
+      <formula1>"BOTH,PERFORMANCE_BASED,DETACHED_VOLUME"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -22529,45 +23037,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>720</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="94" t="s">
-        <v>674</v>
-      </c>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="95"/>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="95"/>
-      <c r="AI1" s="95"/>
+      <c r="A1" s="100" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="111" t="s">
+        <v>662</v>
+      </c>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="112"/>
+      <c r="Z1" s="112"/>
+      <c r="AA1" s="112"/>
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="112"/>
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="112"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
+      <c r="AI1" s="112"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -22577,103 +23085,103 @@
         <v>6</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="Q2" s="27" t="s">
         <v>67</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="V2" s="27" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="W2" s="27" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="Y2" s="27" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="Z2" s="27" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="AB2" s="27" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="AC2" s="27" t="s">
         <v>72</v>
       </c>
       <c r="AD2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="AE2" s="27" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="AF2" s="27" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="AG2" s="27" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="AH2" s="27" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="AI2" s="27" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -22714,27 +23222,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>675</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>663</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -22744,55 +23252,55 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I2" s="17" t="s">
         <v>74</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -22830,30 +23338,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>676</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="85"/>
+      <c r="A1" s="100" t="s">
+        <v>664</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="102"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -22863,64 +23371,64 @@
         <v>6</v>
       </c>
       <c r="C2" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>499</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="F2" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>511</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>518</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="30" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="L2" s="30" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O2" s="30" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="V2" s="27" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -22955,77 +23463,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>519</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>110</v>
-      </c>
       <c r="D2" s="27" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="M2" s="64" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -23064,84 +23572,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="154" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>272</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="86" t="s">
-        <v>280</v>
-      </c>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="101"/>
+      <c r="A1" s="100" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="103" t="s">
+        <v>268</v>
+      </c>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="115"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="O2" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="P2" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="Q2" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="S2" s="10" t="s">
         <v>22</v>
@@ -23175,13 +23683,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>711</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>699</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -23194,10 +23702,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -23227,33 +23735,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="34" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>677</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
+      <c r="A1" s="97" t="s">
+        <v>665</v>
+      </c>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="105"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>110</v>
-      </c>
       <c r="E2" s="17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -23289,21 +23797,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
-        <v>520</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
+      <c r="A1" s="111" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
     </row>
     <row r="2" spans="1:20" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -23313,40 +23821,40 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>74</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="S2" s="66"/>
       <c r="T2" s="66"/>
@@ -23663,19 +24171,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>520</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
+      <c r="A1" s="100" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -23685,34 +24193,34 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -23747,24 +24255,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="160" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>678</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
+      <c r="A1" s="100" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
     </row>
     <row r="2" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -23774,46 +24282,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="H2" s="68" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="L2" s="43" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="M2" s="42" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O2" s="42" t="s">
         <v>74</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -23876,35 +24384,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>679</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="85"/>
+      <c r="A1" s="100" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="102"/>
     </row>
     <row r="2" spans="1:27" s="41" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="42" t="s">
@@ -23920,73 +24428,73 @@
         <v>29</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F2" s="42" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="K2" s="55" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="L2" s="42" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="M2" s="43" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="R2" s="42" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="S2" s="42" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="T2" s="42" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="U2" s="42" t="s">
         <v>72</v>
       </c>
       <c r="V2" s="42" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="W2" s="42" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="X2" s="42" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="Y2" s="42" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="Z2" s="42" t="s">
         <v>74</v>
       </c>
       <c r="AA2" s="42" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -26991,16 +27499,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>680</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="A1" s="100" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
@@ -27010,7 +27518,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D2" s="55" t="s">
         <v>66</v>
@@ -27019,13 +27527,13 @@
         <v>67</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="H2" s="58" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -29832,29 +30340,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
-        <v>681</v>
-      </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
+      <c r="A1" s="109" t="s">
+        <v>669</v>
+      </c>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
       <c r="V1" s="61"/>
       <c r="W1" s="61"/>
       <c r="X1" s="61"/>
@@ -29867,61 +30375,61 @@
         <v>6</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="J2" s="55" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="K2" s="55" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="L2" s="55" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="M2" s="55" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="N2" s="55" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="O2" s="55" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="P2" s="55" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="Q2" s="55" t="s">
         <v>72</v>
       </c>
       <c r="R2" s="55" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="S2" s="63" t="s">
         <v>74</v>
       </c>
       <c r="T2" s="63" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="U2" s="62" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="V2"/>
       <c r="W2"/>
@@ -34160,26 +34668,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="138" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="103" t="s">
-        <v>729</v>
-      </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="105"/>
+      <c r="A1" s="117" t="s">
+        <v>717</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="119"/>
     </row>
     <row r="2" spans="1:18" s="41" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -34189,52 +34697,52 @@
         <v>6</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="E2" s="64" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="H2" s="64" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="L2" s="79" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="M2" s="79" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="Q2" s="27" t="s">
         <v>72</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -34288,65 +34796,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
-        <v>758</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
+      <c r="A1" s="111" t="s">
+        <v>738</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
     </row>
     <row r="2" spans="1:15" s="34" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>670</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>681</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>682</v>
       </c>
-      <c r="C2" s="64" t="s">
-        <v>693</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>694</v>
-      </c>
       <c r="E2" s="27" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="O2" s="41"/>
     </row>
@@ -34359,7 +34867,7 @@
     </row>
     <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -34399,26 +34907,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="261" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="106" t="s">
-        <v>705</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="108"/>
+      <c r="A1" s="120" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="122"/>
     </row>
     <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -34428,52 +34936,52 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>615</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>616</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>617</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>629</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>620</v>
+      </c>
+      <c r="I2" s="26" t="s">
         <v>627</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>628</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>641</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>640</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>632</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>639</v>
-      </c>
       <c r="J2" s="26" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="R2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -34536,37 +35044,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="34" customFormat="1" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>645</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="82"/>
+      <c r="A1" s="97" t="s">
+        <v>633</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="99"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -35250,6 +35758,1193 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFDE539-E357-DC43-85F1-56944F49BA3A}">
+  <sheetPr>
+    <tabColor rgb="FF009193"/>
+  </sheetPr>
+  <dimension ref="A1:O65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="19.1640625" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="97" t="s">
+        <v>740</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="107" t="s">
+        <v>741</v>
+      </c>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+    </row>
+    <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2" s="93" t="s">
+        <v>743</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2" s="68" t="s">
+        <v>749</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="J2" s="94" t="s">
+        <v>751</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="M2" s="95" t="s">
+        <v>754</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>746</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="96"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="96"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="96"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="96"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="96"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="96"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="96"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="96"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="96"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="96"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="96"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="96"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="96"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="96"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="96"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="96"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="96"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="96"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="96"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="96"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="96"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="96"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="96"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="96"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="96"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="96"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="96"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="96"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A53" s="28"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="96"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
+      <c r="M53" s="96"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="28"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="96"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="96"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55" s="28"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="96"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="96"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="96"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="96"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="96"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="96"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="96"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="96"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="96"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="96"/>
+      <c r="N59" s="28"/>
+      <c r="O59" s="28"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="28"/>
+      <c r="M60" s="96"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="28"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="96"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="96"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="96"/>
+      <c r="K62" s="28"/>
+      <c r="L62" s="28"/>
+      <c r="M62" s="96"/>
+      <c r="N62" s="28"/>
+      <c r="O62" s="28"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="96"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="96"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="96"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="96"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" s="28"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="96"/>
+      <c r="K65" s="28"/>
+      <c r="L65" s="28"/>
+      <c r="M65" s="96"/>
+      <c r="N65" s="28"/>
+      <c r="O65" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:O1"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="I3:I1048576" xr:uid="{D0BA8F91-9738-AF46-992D-051C2BF37ADB}">
+      <formula1>"AES,RSA,ECDSA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K3:K1048576" xr:uid="{33F1DA78-B244-F149-BC6A-6B32092416EC}">
+      <formula1>"NIST_P256,NIST_P384,NIST_P521"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H3:H1048576" xr:uid="{FDF379D8-EF4D-D14B-B2C0-DAAF68E0928C}">
+      <formula1>"HSM,SOFTWARE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D3:D1048576" xr:uid="{67F04A16-70B0-2E44-A905-6CC88BBDCD5C}">
+      <formula1>"default,virtual_private"</formula1>
+    </dataValidation>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="A1:A2 H2:I2 K2 J2:J1048576 B2 C2:C1048576 D2:F2 L2:XFD1048576 P1:XFD1 G2:G1048576 H1" xr:uid="{43FE3EC3-D7B0-D549-840B-6C117E9E2D84}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1F6A15-066C-494D-992B-F6A4A794D67F}">
   <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="28.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -35293,124 +36988,124 @@
   <sheetData>
     <row r="1" spans="1:40" s="46" customFormat="1" ht="148" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="54" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="G1" s="54" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="54" t="s">
+        <v>398</v>
+      </c>
+      <c r="I1" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="L1" s="54" t="s">
+        <v>402</v>
+      </c>
+      <c r="M1" s="54" t="s">
+        <v>449</v>
+      </c>
+      <c r="N1" s="54" t="s">
+        <v>403</v>
+      </c>
+      <c r="O1" s="54" t="s">
+        <v>404</v>
+      </c>
+      <c r="P1" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q1" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>407</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="T1" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="U1" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="V1" s="45" t="s">
         <v>410</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="W1" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="X1" s="45" t="s">
         <v>412</v>
       </c>
-      <c r="K1" s="54" t="s">
-        <v>413</v>
-      </c>
-      <c r="L1" s="54" t="s">
-        <v>414</v>
-      </c>
-      <c r="M1" s="54" t="s">
-        <v>461</v>
-      </c>
-      <c r="N1" s="54" t="s">
-        <v>415</v>
-      </c>
-      <c r="O1" s="54" t="s">
-        <v>416</v>
-      </c>
-      <c r="P1" s="54" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q1" s="54" t="s">
-        <v>418</v>
-      </c>
-      <c r="R1" s="54" t="s">
-        <v>419</v>
-      </c>
-      <c r="S1" s="54" t="s">
-        <v>420</v>
-      </c>
-      <c r="T1" s="54" t="s">
-        <v>463</v>
-      </c>
-      <c r="U1" s="54" t="s">
-        <v>421</v>
-      </c>
-      <c r="V1" s="45" t="s">
-        <v>422</v>
-      </c>
-      <c r="W1" s="45" t="s">
-        <v>423</v>
-      </c>
-      <c r="X1" s="45" t="s">
-        <v>424</v>
-      </c>
       <c r="Y1" s="54" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="Z1" s="45" t="s">
         <v>67</v>
       </c>
       <c r="AA1" s="45" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="AB1" s="45" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="AC1" s="45" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="AD1" s="45" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AE1" s="45" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="AF1" s="45" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="AG1" s="45" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AH1" s="45" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="AI1" s="45" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="AJ1" s="45" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="AK1" s="45" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="AL1" s="45" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="AM1" s="45" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="AN1" s="45" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="0.2">
@@ -35418,22 +37113,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="C2" s="47" t="s">
+        <v>582</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>585</v>
+      </c>
+      <c r="E2" s="47" t="s">
         <v>594</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>597</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>606</v>
       </c>
       <c r="F2" s="48" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="H2" s="48" t="s">
         <v>28</v>
@@ -35445,73 +37140,73 @@
         <v>43</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="L2" s="48" t="s">
         <v>20</v>
       </c>
       <c r="M2" s="48" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="N2" s="48" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="O2" s="48" t="s">
         <v>63</v>
       </c>
       <c r="P2" s="49" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="Q2" s="48" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="R2" s="48" t="s">
         <v>42</v>
       </c>
       <c r="S2" s="48" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="T2" s="48" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="U2" s="48" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="V2" s="48" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="W2" s="48" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="X2" s="48" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="Y2" s="48" t="b">
         <v>1</v>
       </c>
       <c r="Z2" s="48" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AA2" s="48" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="AB2" s="48" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AC2" s="48" t="s">
         <v>20</v>
       </c>
       <c r="AD2" s="48" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AE2" s="48" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="AF2" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="AG2" s="48" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="AH2" s="48">
         <v>301</v>
@@ -35520,19 +37215,19 @@
         <v>8</v>
       </c>
       <c r="AJ2" s="48" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AK2" s="47" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="AL2" s="47" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="AM2" s="47" t="b">
         <v>0</v>
       </c>
       <c r="AN2" s="47" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="0.2">
@@ -35540,22 +37235,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C3" s="47" t="s">
+        <v>583</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>586</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>595</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>598</v>
-      </c>
-      <c r="E3" s="47" t="s">
-        <v>607</v>
       </c>
       <c r="F3" s="48" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="H3" s="48" t="s">
         <v>27</v>
@@ -35564,7 +37259,7 @@
         <v>42</v>
       </c>
       <c r="J3" s="48" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="K3" s="48"/>
       <c r="L3" s="48" t="s">
@@ -35572,10 +37267,10 @@
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="O3" s="48" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>64</v>
@@ -35587,47 +37282,47 @@
         <v>69</v>
       </c>
       <c r="S3" s="48" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="T3" s="48" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="U3" s="48"/>
       <c r="V3" s="48" t="s">
         <v>84</v>
       </c>
       <c r="W3" s="48" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="X3" s="48" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="Y3" s="48" t="b">
         <v>0</v>
       </c>
       <c r="Z3" s="48" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="AA3" s="48" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AB3" s="48" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="AC3" s="48" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AD3" s="48" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="AE3" s="48" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="AF3" s="50" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="AG3" s="48" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="AH3" s="48">
         <v>302</v>
@@ -35636,19 +37331,19 @@
         <v>16</v>
       </c>
       <c r="AJ3" s="48" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="AK3" s="47" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="AL3" s="47" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="AM3" s="47" t="b">
         <v>1</v>
       </c>
       <c r="AN3" s="47" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="0.2">
@@ -35656,20 +37351,20 @@
         <v>5</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="C4" s="47" t="s">
+        <v>584</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>587</v>
+      </c>
+      <c r="E4" s="47" t="s">
         <v>596</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>599</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>608</v>
       </c>
       <c r="F4" s="48"/>
       <c r="G4" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H4" s="48"/>
       <c r="I4" s="48" t="s">
@@ -35678,7 +37373,7 @@
       <c r="J4" s="48"/>
       <c r="K4" s="48"/>
       <c r="L4" s="48" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="M4" s="48"/>
       <c r="N4" s="48"/>
@@ -35693,39 +37388,39 @@
         <v>76</v>
       </c>
       <c r="S4" s="48" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="T4" s="48" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="U4" s="48"/>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
       <c r="X4" s="48" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="Y4" s="48"/>
       <c r="Z4" s="48" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AA4" s="48" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="AB4" s="48"/>
       <c r="AC4" s="48" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="AD4" s="48" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="AE4" s="48" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AF4" s="50" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AG4" s="48" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AH4" s="48">
         <v>303</v>
@@ -35734,7 +37429,7 @@
         <v>32</v>
       </c>
       <c r="AN4" s="47" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="0.2">
@@ -35742,14 +37437,14 @@
         <v>6</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="H5" s="48"/>
       <c r="I5" s="48" t="s">
@@ -35761,7 +37456,7 @@
       <c r="M5" s="48"/>
       <c r="N5" s="48"/>
       <c r="O5" s="48" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="P5" s="49"/>
       <c r="Q5" s="48"/>
@@ -35772,19 +37467,19 @@
       <c r="X5" s="48"/>
       <c r="Y5" s="48"/>
       <c r="Z5" s="48" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="AA5" s="48"/>
       <c r="AB5" s="48"/>
       <c r="AC5" s="48"/>
       <c r="AD5" s="48" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="AE5" s="48" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="AF5" s="50" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="AG5" s="48"/>
       <c r="AH5" s="48">
@@ -35799,14 +37494,14 @@
         <v>7</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="H6" s="48"/>
       <c r="I6" s="48"/>
@@ -35831,10 +37526,10 @@
       <c r="AB6" s="48"/>
       <c r="AC6" s="48"/>
       <c r="AD6" s="48" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="AE6" s="48" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="AF6" s="51"/>
       <c r="AG6" s="48"/>
@@ -35848,14 +37543,14 @@
         <v>8</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="H7" s="48"/>
       <c r="I7" s="48"/>
@@ -35880,10 +37575,10 @@
       <c r="AB7" s="48"/>
       <c r="AC7" s="48"/>
       <c r="AD7" s="48" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AE7" s="48" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="AF7" s="51"/>
       <c r="AG7" s="48"/>
@@ -35895,14 +37590,14 @@
         <v>9</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="F8" s="48"/>
       <c r="G8" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="H8" s="48"/>
       <c r="I8" s="48"/>
@@ -35927,10 +37622,10 @@
       <c r="AB8" s="48"/>
       <c r="AC8" s="48"/>
       <c r="AD8" s="48" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="AE8" s="48" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="AF8" s="51"/>
       <c r="AG8" s="48"/>
@@ -35942,14 +37637,14 @@
         <v>10</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F9" s="48"/>
       <c r="G9" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="H9" s="48"/>
       <c r="I9" s="48"/>
@@ -35974,10 +37669,10 @@
       <c r="AB9" s="48"/>
       <c r="AC9" s="48"/>
       <c r="AD9" s="48" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="AE9" s="48" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="AF9" s="51"/>
       <c r="AG9" s="48"/>
@@ -35989,14 +37684,14 @@
         <v>11</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="H10" s="48"/>
       <c r="I10" s="48"/>
@@ -36021,10 +37716,10 @@
       <c r="AB10" s="48"/>
       <c r="AC10" s="48"/>
       <c r="AD10" s="48" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="AE10" s="48" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="AF10" s="51"/>
       <c r="AG10" s="48"/>
@@ -36036,14 +37731,14 @@
         <v>12</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="F11" s="48"/>
       <c r="G11" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="H11" s="48"/>
       <c r="I11" s="48"/>
@@ -36068,10 +37763,10 @@
       <c r="AB11" s="48"/>
       <c r="AC11" s="48"/>
       <c r="AD11" s="48" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AE11" s="48" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="AF11" s="51"/>
       <c r="AG11" s="48"/>
@@ -36084,7 +37779,7 @@
       </c>
       <c r="F12" s="48"/>
       <c r="G12" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="H12" s="48"/>
       <c r="I12" s="48"/>
@@ -36110,7 +37805,7 @@
       <c r="AC12" s="48"/>
       <c r="AD12" s="48"/>
       <c r="AE12" s="48" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="AF12" s="51"/>
       <c r="AG12" s="48"/>
@@ -36123,7 +37818,7 @@
       </c>
       <c r="F13" s="48"/>
       <c r="G13" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="H13" s="48"/>
       <c r="I13" s="48"/>
@@ -36149,7 +37844,7 @@
       <c r="AC13" s="48"/>
       <c r="AD13" s="48"/>
       <c r="AE13" s="48" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="AF13" s="51"/>
       <c r="AG13" s="48"/>
@@ -36162,7 +37857,7 @@
       </c>
       <c r="F14" s="48"/>
       <c r="G14" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="H14" s="48"/>
       <c r="I14" s="48"/>
@@ -36188,7 +37883,7 @@
       <c r="AC14" s="48"/>
       <c r="AD14" s="48"/>
       <c r="AE14" s="48" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AF14" s="51"/>
       <c r="AG14" s="48"/>
@@ -36201,7 +37896,7 @@
       </c>
       <c r="F15" s="48"/>
       <c r="G15" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="H15" s="48"/>
       <c r="I15" s="48"/>
@@ -36227,7 +37922,7 @@
       <c r="AC15" s="48"/>
       <c r="AD15" s="48"/>
       <c r="AE15" s="48" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="AF15" s="51"/>
       <c r="AG15" s="48"/>
@@ -36240,7 +37935,7 @@
       </c>
       <c r="F16" s="48"/>
       <c r="G16" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H16" s="48"/>
       <c r="I16" s="48"/>
@@ -36266,7 +37961,7 @@
       <c r="AC16" s="48"/>
       <c r="AD16" s="48"/>
       <c r="AE16" s="48" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="AF16" s="51"/>
       <c r="AG16" s="48"/>
@@ -36279,7 +37974,7 @@
       </c>
       <c r="F17" s="48"/>
       <c r="G17" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="H17" s="48"/>
       <c r="I17" s="48"/>
@@ -36305,7 +38000,7 @@
       <c r="AC17" s="48"/>
       <c r="AD17" s="48"/>
       <c r="AE17" s="48" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="AF17" s="51"/>
       <c r="AG17" s="48"/>
@@ -36318,7 +38013,7 @@
       </c>
       <c r="F18" s="48"/>
       <c r="G18" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="H18" s="48"/>
       <c r="I18" s="48"/>
@@ -36344,7 +38039,7 @@
       <c r="AC18" s="48"/>
       <c r="AD18" s="48"/>
       <c r="AE18" s="48" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AF18" s="51"/>
       <c r="AG18" s="48"/>
@@ -36357,7 +38052,7 @@
       </c>
       <c r="F19" s="48"/>
       <c r="G19" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="H19" s="48"/>
       <c r="I19" s="48"/>
@@ -36383,7 +38078,7 @@
       <c r="AC19" s="48"/>
       <c r="AD19" s="48"/>
       <c r="AE19" s="48" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AF19" s="51"/>
       <c r="AG19" s="48"/>
@@ -36396,7 +38091,7 @@
       </c>
       <c r="F20" s="48"/>
       <c r="G20" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="H20" s="48"/>
       <c r="I20" s="48"/>
@@ -36422,7 +38117,7 @@
       <c r="AC20" s="48"/>
       <c r="AD20" s="48"/>
       <c r="AE20" s="48" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="AF20" s="51"/>
       <c r="AG20" s="48"/>
@@ -36435,7 +38130,7 @@
       </c>
       <c r="F21" s="48"/>
       <c r="G21" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="H21" s="48"/>
       <c r="I21" s="48"/>
@@ -36461,7 +38156,7 @@
       <c r="AC21" s="48"/>
       <c r="AD21" s="48"/>
       <c r="AE21" s="48" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="AF21" s="51"/>
       <c r="AG21" s="48"/>
@@ -36474,7 +38169,7 @@
       </c>
       <c r="F22" s="48"/>
       <c r="G22" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="H22" s="48"/>
       <c r="I22" s="48"/>
@@ -36500,7 +38195,7 @@
       <c r="AC22" s="48"/>
       <c r="AD22" s="48"/>
       <c r="AE22" s="48" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AF22" s="51"/>
       <c r="AG22" s="48"/>
@@ -36513,7 +38208,7 @@
       </c>
       <c r="F23" s="48"/>
       <c r="G23" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
@@ -36539,7 +38234,7 @@
       <c r="AC23" s="48"/>
       <c r="AD23" s="48"/>
       <c r="AE23" s="48" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="AF23" s="51"/>
       <c r="AG23" s="48"/>
@@ -36552,7 +38247,7 @@
       </c>
       <c r="F24" s="48"/>
       <c r="G24" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="H24" s="48"/>
       <c r="I24" s="48"/>
@@ -36578,7 +38273,7 @@
       <c r="AC24" s="48"/>
       <c r="AD24" s="48"/>
       <c r="AE24" s="48" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="AF24" s="51"/>
       <c r="AG24" s="48"/>
@@ -36591,7 +38286,7 @@
       </c>
       <c r="F25" s="48"/>
       <c r="G25" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
@@ -36617,7 +38312,7 @@
       <c r="AC25" s="48"/>
       <c r="AD25" s="48"/>
       <c r="AE25" s="48" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AF25" s="51"/>
       <c r="AG25" s="48"/>
@@ -36630,7 +38325,7 @@
       </c>
       <c r="F26" s="48"/>
       <c r="G26" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="H26" s="48"/>
       <c r="I26" s="48"/>
@@ -36656,7 +38351,7 @@
       <c r="AC26" s="48"/>
       <c r="AD26" s="48"/>
       <c r="AE26" s="48" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="AF26" s="51"/>
       <c r="AG26" s="48"/>
@@ -36669,7 +38364,7 @@
       </c>
       <c r="F27" s="48"/>
       <c r="G27" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="H27" s="48"/>
       <c r="I27" s="48"/>
@@ -36695,7 +38390,7 @@
       <c r="AC27" s="48"/>
       <c r="AD27" s="48"/>
       <c r="AE27" s="48" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="AF27" s="51"/>
       <c r="AG27" s="48"/>
@@ -36708,7 +38403,7 @@
       </c>
       <c r="F28" s="48"/>
       <c r="G28" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="H28" s="48"/>
       <c r="I28" s="48"/>
@@ -36734,7 +38429,7 @@
       <c r="AC28" s="48"/>
       <c r="AD28" s="48"/>
       <c r="AE28" s="48" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="AF28" s="51"/>
       <c r="AG28" s="48"/>
@@ -36747,7 +38442,7 @@
       </c>
       <c r="F29" s="48"/>
       <c r="G29" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="H29" s="48"/>
       <c r="I29" s="48"/>
@@ -36773,7 +38468,7 @@
       <c r="AC29" s="48"/>
       <c r="AD29" s="48"/>
       <c r="AE29" s="48" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="AF29" s="51"/>
       <c r="AG29" s="48"/>
@@ -36786,7 +38481,7 @@
       </c>
       <c r="F30" s="48"/>
       <c r="G30" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="H30" s="48"/>
       <c r="I30" s="48"/>
@@ -36812,7 +38507,7 @@
       <c r="AC30" s="48"/>
       <c r="AD30" s="48"/>
       <c r="AE30" s="48" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AF30" s="51"/>
       <c r="AG30" s="48"/>
@@ -36825,7 +38520,7 @@
       </c>
       <c r="F31" s="48"/>
       <c r="G31" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="H31" s="48"/>
       <c r="I31" s="48"/>
@@ -36851,7 +38546,7 @@
       <c r="AC31" s="48"/>
       <c r="AD31" s="48"/>
       <c r="AE31" s="48" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AF31" s="51"/>
       <c r="AG31" s="48"/>
@@ -36890,7 +38585,7 @@
       <c r="AC32" s="48"/>
       <c r="AD32" s="48"/>
       <c r="AE32" s="48" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="AF32" s="51"/>
       <c r="AG32" s="48"/>
@@ -36903,7 +38598,7 @@
       </c>
       <c r="F33" s="48"/>
       <c r="G33" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="H33" s="48"/>
       <c r="I33" s="48"/>
@@ -36929,7 +38624,7 @@
       <c r="AC33" s="48"/>
       <c r="AD33" s="48"/>
       <c r="AE33" s="48" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="AF33" s="51"/>
       <c r="AG33" s="48"/>
@@ -36942,7 +38637,7 @@
       </c>
       <c r="F34" s="48"/>
       <c r="G34" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="H34" s="48"/>
       <c r="I34" s="48"/>
@@ -36968,7 +38663,7 @@
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AE34" s="48" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="AF34" s="51"/>
       <c r="AG34" s="48"/>
@@ -36981,7 +38676,7 @@
       </c>
       <c r="F35" s="48"/>
       <c r="G35" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="H35" s="48"/>
       <c r="I35" s="48"/>
@@ -37007,7 +38702,7 @@
       <c r="AC35" s="48"/>
       <c r="AD35" s="48"/>
       <c r="AE35" s="48" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AF35" s="51"/>
       <c r="AG35" s="48"/>
@@ -37020,7 +38715,7 @@
       </c>
       <c r="F36" s="48"/>
       <c r="G36" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="H36" s="48"/>
       <c r="I36" s="48"/>
@@ -37046,7 +38741,7 @@
       <c r="AC36" s="48"/>
       <c r="AD36" s="48"/>
       <c r="AE36" s="48" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="AF36" s="51"/>
       <c r="AG36" s="48"/>
@@ -37059,7 +38754,7 @@
       </c>
       <c r="F37" s="48"/>
       <c r="G37" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="H37" s="48"/>
       <c r="I37" s="48"/>
@@ -37085,7 +38780,7 @@
       <c r="AC37" s="48"/>
       <c r="AD37" s="48"/>
       <c r="AE37" s="48" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="AF37" s="51"/>
       <c r="AG37" s="48"/>
@@ -37098,7 +38793,7 @@
       </c>
       <c r="F38" s="48"/>
       <c r="G38" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="H38" s="48"/>
       <c r="I38" s="48"/>
@@ -37124,7 +38819,7 @@
       <c r="AC38" s="48"/>
       <c r="AD38" s="48"/>
       <c r="AE38" s="48" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="AF38" s="51"/>
       <c r="AG38" s="48"/>
@@ -37137,7 +38832,7 @@
       </c>
       <c r="F39" s="48"/>
       <c r="G39" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="H39" s="48"/>
       <c r="I39" s="48"/>
@@ -37163,7 +38858,7 @@
       <c r="AC39" s="48"/>
       <c r="AD39" s="48"/>
       <c r="AE39" s="48" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="AF39" s="51"/>
       <c r="AG39" s="48"/>
@@ -37176,7 +38871,7 @@
       </c>
       <c r="F40" s="48"/>
       <c r="G40" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="H40" s="48"/>
       <c r="I40" s="48"/>
@@ -37201,7 +38896,7 @@
       <c r="AC40" s="48"/>
       <c r="AD40" s="48"/>
       <c r="AE40" s="48" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AF40" s="51"/>
       <c r="AG40" s="48"/>
@@ -37213,7 +38908,7 @@
         <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="K41" s="48"/>
       <c r="M41" s="48"/>
@@ -37226,7 +38921,7 @@
         <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="K42" s="48"/>
       <c r="M42" s="48"/>
@@ -37238,7 +38933,7 @@
         <v>44</v>
       </c>
       <c r="G43" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="K43" s="48"/>
       <c r="M43" s="48"/>
@@ -37250,7 +38945,7 @@
         <v>45</v>
       </c>
       <c r="G44" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="K44" s="48"/>
       <c r="M44" s="48"/>
@@ -37311,7 +39006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA888738-FD14-FB42-ABBC-C0E1A08096C4}">
   <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -37332,40 +39027,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C1" s="38" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I1" s="57" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="J1" s="57" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="L1" s="38" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="M1" s="38"/>
     </row>
@@ -37374,740 +39069,740 @@
         <v>78</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="I2" s="28">
         <v>80</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="K2" s="29">
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="56" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="I3" s="28">
         <v>40</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="K3" s="29">
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="56" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="D4" s="29"/>
       <c r="E4" s="29" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="F4" s="29"/>
       <c r="H4" s="8" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="L4" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="56" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D5" s="29"/>
       <c r="E5" s="29" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="F5" s="29"/>
       <c r="H5" s="29" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="L5" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B6" s="29"/>
       <c r="C6" s="29" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6" s="29" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="F6" s="29"/>
       <c r="H6" s="29" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="56" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="29" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="D7" s="29"/>
       <c r="E7" s="29" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F7" s="29"/>
       <c r="H7" s="29" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="56" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="D8" s="29"/>
       <c r="E8" s="29" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="F8" s="29"/>
       <c r="H8" s="29" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="56" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="29" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F9" s="29"/>
       <c r="H9" s="29" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="56" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10" s="29" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F10" s="29"/>
       <c r="H10" s="29" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="56" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="29" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="29" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F11" s="29"/>
       <c r="H11" s="29" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="56" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="29" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="29" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="F12" s="29"/>
       <c r="H12" s="29" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="56" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="29" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="F13" s="29"/>
       <c r="H13" s="29" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="56" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
       <c r="H14" s="29" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H15" s="29" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H16" s="29" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H17" s="29" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H18" s="29" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H19" s="29" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H20" s="29" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H21" s="29" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H22" s="29" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H23" s="29" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H24" s="29" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H25" s="29" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H26" s="29" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H27" s="29" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H28" s="29" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H29" s="29" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H30" s="29" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H31" s="29" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H32" s="29" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H33" s="29" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H34" s="29" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H35" s="29" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H36" s="29" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H37" s="29" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H38" s="29" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H39" s="29" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H40" s="29" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H41" s="29" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H42" s="29" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H43" s="29" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H44" s="29" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H45" s="29" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H46" s="29" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H47" s="29" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H48" s="29" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H49" s="29" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H50" s="29" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H51" s="29" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H52" s="29" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H53" s="29" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H54" s="29" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H55" s="29" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H56" s="29" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H57" s="29" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H58" s="29" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H59" s="29" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H60" s="29" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H61" s="29" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H62" s="29" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H63" s="29" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H64" s="29" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H65" s="29" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H66" s="29" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H67" s="29" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H68" s="29" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H69" s="29" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H70" s="29" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H71" s="29" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H72" s="29" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H73" s="29" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H74" s="29" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H75" s="29" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H76" s="29" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H77" s="29" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H78" s="29" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H79" s="29" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H80" s="29" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H81" s="29" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H82" s="29" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H83" s="29" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H84" s="29" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H85" s="29" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H86" s="29" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H87" s="29" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H88" s="29" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H89" s="29" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H90" s="29" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H91" s="29" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H92" s="29" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H93" s="29" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H94" s="29" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H95" s="29" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H96" s="29" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H97" s="29" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H98" s="29" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H99" s="29" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H100" s="29" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H101" s="29" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H102" s="29" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H103" s="29" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H104" s="29" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H105" s="29" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H106" s="29" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H107" s="29" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H108" s="29" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -38116,7 +39811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17EB8E8D-A5C8-594F-A88C-DAE4B19E97E0}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -38131,36 +39826,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B1" s="69" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C1" s="70" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E1" s="70" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E2" s="20">
         <v>301</v>
@@ -38171,16 +39866,16 @@
     </row>
     <row r="3" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E3" s="25">
         <v>302</v>
@@ -38191,16 +39886,16 @@
     </row>
     <row r="4" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25">
         <v>303</v>
@@ -38211,13 +39906,13 @@
     </row>
     <row r="5" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="25">
@@ -38229,10 +39924,10 @@
     </row>
     <row r="6" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C6" s="19"/>
       <c r="E6" s="25">
@@ -38242,189 +39937,189 @@
     </row>
     <row r="7" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
       <c r="B12" s="25" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="25" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="25" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="25" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="25" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="25" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="25" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="25" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="25" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="25" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="25" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="25" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="25" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="25" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="25" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="25" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="25" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="25" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="25" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="25" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="25" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="25" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="25" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="25" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="25" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="25" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="25" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="25" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="25" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -38436,7 +40131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88501A0A-1A58-D742-9359-905ECDDDA493}">
   <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -38447,16 +40142,16 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="45" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="47"/>
       <c r="B2" s="47" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -38464,7 +40159,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -38472,7 +40167,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -38480,7 +40175,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -38488,7 +40183,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -38779,14 +40474,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="34" customFormat="1" ht="131.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>710</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="82"/>
+      <c r="A1" s="97" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -38799,13 +40494,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -40375,16 +42070,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="34" customFormat="1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>646</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
     </row>
     <row r="2" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -40409,7 +42104,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -42718,19 +44413,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="169" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
-        <v>460</v>
-      </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="86" t="s">
-        <v>647</v>
-      </c>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
+      <c r="A1" s="100" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="103" t="s">
+        <v>635</v>
+      </c>
+      <c r="H1" s="104"/>
+      <c r="I1" s="105"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
@@ -42740,25 +44435,25 @@
         <v>6</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -42789,29 +44484,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>731</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="A1" s="97" t="s">
+        <v>718</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="110" t="s">
-        <v>732</v>
-      </c>
-      <c r="E2" s="111" t="s">
-        <v>269</v>
+      <c r="D2" s="81" t="s">
+        <v>719</v>
+      </c>
+      <c r="E2" s="82" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -42846,74 +44541,74 @@
     <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="119" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="120" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="120" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="90" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="91" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="91" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="65.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.5" style="121" customWidth="1"/>
+    <col min="14" max="14" width="41.5" style="92" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="34" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>733</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="82"/>
+      <c r="A1" s="97" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="99"/>
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="110" t="s">
-        <v>734</v>
-      </c>
-      <c r="E2" s="111" t="s">
-        <v>735</v>
-      </c>
-      <c r="F2" s="111" t="s">
-        <v>736</v>
-      </c>
-      <c r="G2" s="111" t="s">
-        <v>737</v>
-      </c>
-      <c r="H2" s="112" t="s">
-        <v>738</v>
-      </c>
-      <c r="I2" s="113" t="s">
-        <v>739</v>
-      </c>
-      <c r="J2" s="113" t="s">
-        <v>740</v>
-      </c>
-      <c r="K2" s="111" t="s">
-        <v>741</v>
-      </c>
-      <c r="L2" s="111" t="s">
-        <v>742</v>
-      </c>
-      <c r="M2" s="111" t="s">
-        <v>743</v>
-      </c>
-      <c r="N2" s="114" t="s">
-        <v>269</v>
+      <c r="D2" s="81" t="s">
+        <v>721</v>
+      </c>
+      <c r="E2" s="82" t="s">
+        <v>722</v>
+      </c>
+      <c r="F2" s="82" t="s">
+        <v>723</v>
+      </c>
+      <c r="G2" s="82" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2" s="83" t="s">
+        <v>725</v>
+      </c>
+      <c r="I2" s="84" t="s">
+        <v>726</v>
+      </c>
+      <c r="J2" s="84" t="s">
+        <v>727</v>
+      </c>
+      <c r="K2" s="82" t="s">
+        <v>728</v>
+      </c>
+      <c r="L2" s="82" t="s">
+        <v>729</v>
+      </c>
+      <c r="M2" s="82" t="s">
+        <v>730</v>
+      </c>
+      <c r="N2" s="85" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.2">
@@ -42924,9 +44619,9 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
       <c r="K3" s="28"/>
       <c r="L3" s="28"/>
       <c r="M3" s="28"/>
@@ -42940,13 +44635,13 @@
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
       <c r="K4" s="28"/>
-      <c r="L4" s="117"/>
+      <c r="L4" s="88"/>
       <c r="M4" s="28"/>
-      <c r="N4" s="118"/>
+      <c r="N4" s="89"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="28"/>
@@ -42956,13 +44651,13 @@
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
       <c r="G5" s="28"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
       <c r="K5" s="28"/>
       <c r="L5" s="29"/>
       <c r="M5" s="28"/>
-      <c r="N5" s="118"/>
+      <c r="N5" s="89"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="28"/>
@@ -42972,13 +44667,13 @@
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
       <c r="K6" s="28"/>
       <c r="L6" s="29"/>
       <c r="M6" s="28"/>
-      <c r="N6" s="118"/>
+      <c r="N6" s="89"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="28"/>
@@ -42988,13 +44683,13 @@
       <c r="E7" s="28"/>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="116"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
       <c r="K7" s="28"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
-      <c r="N7" s="118"/>
+      <c r="N7" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19569292-BC0A-B14D-B0E7-0CBCFE65E647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE011F5-6BF6-964D-BE2C-54919FBFB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6940" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -373,7 +373,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
+          <t>Mandatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
         </r>
       </text>
     </comment>
@@ -382,30 +382,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Suruchi</author>
-  </authors>
-  <commentList>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{DFA3381A-B6E3-8642-9D9B-F59DB2F382DA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
@@ -650,7 +626,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -712,7 +688,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="775">
   <si>
     <t>Region</t>
   </si>
@@ -10327,12 +10303,318 @@
   <si>
     <t>Matching Rule</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Default value for columns if left blank: sourceCIDR- 0.0.0.0/0, Access- READ_WRITE, GID- 65534, UID- 65534, IDSquash- NONE and Require PS Port- false.
+Mount target IP will take default values from OCI if left blank.
+Resources will be created based on 'MountTarget Name' and 'FSS Name' columns.
+Below sample data shows example of  multiple FSS(FSS1 and FSS2) using single MT(MT1) , 1 FSS(FSS3) using multiple MTs(MT2 and MT3) and also 1 FSS(FSS4) using 1 MT(MT4).</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onlyMT is Mount target without any FSS. onlyFSS is File System without any Mount Target or Export (used for replication)</t>
+    </r>
+  </si>
+  <si>
+    <t>MountTarget Name</t>
+  </si>
+  <si>
+    <t>MountTarget SubnetName</t>
+  </si>
+  <si>
+    <t>MountTarget IP</t>
+  </si>
+  <si>
+    <t>MountTarget Hostname</t>
+  </si>
+  <si>
+    <t>FSS Name</t>
+  </si>
+  <si>
+    <t>Source Snapshot</t>
+  </si>
+  <si>
+    <t>Snapshot Policy</t>
+  </si>
+  <si>
+    <t>Replication Information</t>
+  </si>
+  <si>
+    <t>Source CIDR</t>
+  </si>
+  <si>
+    <t>Access (READ_ONLY|READ_WRITE)</t>
+  </si>
+  <si>
+    <t>GID</t>
+  </si>
+  <si>
+    <t>UID</t>
+  </si>
+  <si>
+    <t>IDSquash (NONE|ALL|ROOT)</t>
+  </si>
+  <si>
+    <t>Require PS Port (true|false)</t>
+  </si>
+  <si>
+    <t>Is Anonymous Access Allowed</t>
+  </si>
+  <si>
+    <t>Allowed Auth</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
+Freeform and Defined Tags - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter subnet name as : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Source Snapshot:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Snapshot Policy - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accepts OCID of the snapshot policy or the name in format: &lt;snaphot_policy_compartment_name&gt;@&lt;snaphost_policy_name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Replication Information: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Defined Tags" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10658,6 +10940,15 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -10924,7 +11215,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -11203,6 +11494,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -22871,11 +23171,11 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -22887,8 +23187,8 @@
     <col min="8" max="8" width="8.5" customWidth="1"/>
     <col min="9" max="9" width="9.83203125" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" customWidth="1"/>
-    <col min="12" max="12" width="7.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="8.5" customWidth="1"/>
     <col min="14" max="14" width="17.1640625" customWidth="1"/>
     <col min="15" max="15" width="15.5" customWidth="1"/>
@@ -22896,9 +23196,9 @@
     <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="97" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -22910,84 +23210,99 @@
       <c r="I1" s="98"/>
       <c r="J1" s="98"/>
       <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="101"/>
-    </row>
-    <row r="2" spans="1:18" s="33" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="113" t="s">
+        <v>757</v>
+      </c>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="115"/>
+    </row>
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>655</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>81</v>
+      <c r="C2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>758</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>759</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>66</v>
+        <v>760</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>82</v>
+        <v>761</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>503</v>
+        <v>762</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>262</v>
+        <v>763</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>725</v>
+        <v>764</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>726</v>
+        <v>765</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>727</v>
+        <v>85</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>728</v>
+        <v>766</v>
       </c>
       <c r="O2" s="26" t="s">
-        <v>502</v>
+        <v>767</v>
       </c>
       <c r="P2" s="26" t="s">
-        <v>73</v>
+        <v>768</v>
       </c>
       <c r="Q2" s="26" t="s">
-        <v>377</v>
+        <v>769</v>
       </c>
       <c r="R2" s="26" t="s">
+        <v>770</v>
+      </c>
+      <c r="S2" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>772</v>
+      </c>
+      <c r="U2" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="V2" s="26" t="s">
         <v>258</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="M1:V1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="1" sqref="A3:XFD1048576 A1:J2 L1:M2 O1:XFD2 N1" xr:uid="{02462EBB-6C3D-AD4C-90E1-0F01761ACD92}"/>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="N2" xr:uid="{44F44AA6-F9A2-F043-9A7C-E9C593C12245}"/>
-    <dataValidation type="list" sqref="K1:K2" xr:uid="{296BAB61-C7D2-7746-8608-28C808FD0978}">
-      <formula1>"BOTH,PERFORMANCE_BASED,DETACHED_VOLUME"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" sqref="A3:XFD1048576 U1:XFD2 B2:L2 M1:S2 A1:A2" xr:uid="{02462EBB-6C3D-AD4C-90E1-0F01761ACD92}"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="T1:T2" xr:uid="{7A2F3F2A-4835-1545-9D47-36E98CCE349F}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -23585,15 +23900,15 @@
       <c r="J1" s="102" t="s">
         <v>267</v>
       </c>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="114"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="117"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -31238,26 +31553,26 @@
       <c r="A1" s="108" t="s">
         <v>663</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
       <c r="V1" s="60"/>
       <c r="W1" s="60"/>
       <c r="X1" s="60"/>
@@ -35563,26 +35878,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="138" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="119" t="s">
         <v>710</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="118"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="121"/>
     </row>
     <row r="2" spans="1:18" s="40" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -35802,26 +36117,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="261" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="122" t="s">
         <v>687</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="124"/>
     </row>
     <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE011F5-6BF6-964D-BE2C-54919FBFB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB637C2C-B53B-494C-AA72-9F0D821894C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6940" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -8418,265 +8418,6 @@
     <t>Quota Policy</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"Region" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Home Region only</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Scope" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Compartment or Tag</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Target" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Compartment Name or {tagNamespace}.{tagKey}.{tagValue}. Note- It should be a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cost Tracking Tag.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Schedule" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MONTH or  SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Amount" - T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Start Day" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Budget Start Date"/"Budget End Date" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Rules" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Recipients": </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> comma seperated email addresses
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                                </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -10595,6 +10336,254 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"Region" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home Region only</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Scope" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment or Tag</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Target" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment Name or {tagNamespace}.{tagKey}.{tagValue}.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Schedule" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONTH or  SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Amount" - T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Start Day" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Budget Start Date"/"Budget End Date" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Rules" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Recipients": </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> comma seperated email addresses
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                                </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -16734,7 +16723,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -16765,7 +16754,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="97" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -23077,7 +23066,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="97" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -23129,16 +23118,16 @@
         <v>262</v>
       </c>
       <c r="K2" s="26" t="s">
+        <v>724</v>
+      </c>
+      <c r="L2" s="26" t="s">
         <v>725</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="26" t="s">
         <v>726</v>
       </c>
-      <c r="M2" s="26" t="s">
+      <c r="N2" s="26" t="s">
         <v>727</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>728</v>
       </c>
       <c r="O2" s="26" t="s">
         <v>502</v>
@@ -23198,7 +23187,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="97" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -23212,7 +23201,7 @@
       <c r="K1" s="98"/>
       <c r="L1" s="101"/>
       <c r="M1" s="113" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="N1" s="114"/>
       <c r="O1" s="114"/>
@@ -23235,58 +23224,58 @@
         <v>66</v>
       </c>
       <c r="D2" s="26" t="s">
+        <v>757</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>758</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>759</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>760</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>761</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>74</v>
       </c>
       <c r="I2" s="26" t="s">
+        <v>761</v>
+      </c>
+      <c r="J2" s="26" t="s">
         <v>762</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="K2" s="26" t="s">
         <v>763</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="L2" s="26" t="s">
         <v>764</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>765</v>
       </c>
       <c r="M2" s="26" t="s">
         <v>85</v>
       </c>
       <c r="N2" s="26" t="s">
+        <v>765</v>
+      </c>
+      <c r="O2" s="26" t="s">
         <v>766</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="P2" s="26" t="s">
         <v>767</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="Q2" s="26" t="s">
         <v>768</v>
       </c>
-      <c r="Q2" s="26" t="s">
+      <c r="R2" s="26" t="s">
         <v>769</v>
       </c>
-      <c r="R2" s="26" t="s">
+      <c r="S2" s="26" t="s">
         <v>770</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="T2" s="26" t="s">
         <v>771</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="U2" s="26" t="s">
         <v>772</v>
-      </c>
-      <c r="U2" s="26" t="s">
-        <v>773</v>
       </c>
       <c r="V2" s="26" t="s">
         <v>258</v>
@@ -23999,7 +23988,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="33" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="96" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -24017,7 +24006,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>258</v>
@@ -25415,10 +25404,10 @@
         <v>513</v>
       </c>
       <c r="G2" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>729</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>730</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>102</v>
@@ -36007,7 +35996,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="110" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B1" s="111"/>
       <c r="C1" s="111"/>
@@ -36256,7 +36245,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="33" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="97" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B1" s="98"/>
       <c r="C1" s="98"/>
@@ -36273,16 +36262,16 @@
         <v>609</v>
       </c>
       <c r="C2" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>752</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>753</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>754</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>258</v>
@@ -37221,7 +37210,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="96" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -37230,7 +37219,7 @@
       <c r="F1" s="96"/>
       <c r="G1" s="96"/>
       <c r="H1" s="106" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I1" s="96"/>
       <c r="J1" s="96"/>
@@ -37245,46 +37234,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="C2" s="92" t="s">
         <v>735</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="D2" s="16" t="s">
         <v>736</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>737</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>740</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>741</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>742</v>
+      </c>
+      <c r="J2" s="93" t="s">
+        <v>743</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="M2" s="94" t="s">
+        <v>746</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>738</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>740</v>
-      </c>
-      <c r="G2" s="41" t="s">
-        <v>741</v>
-      </c>
-      <c r="H2" s="67" t="s">
-        <v>742</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>743</v>
-      </c>
-      <c r="J2" s="93" t="s">
-        <v>744</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>745</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>746</v>
-      </c>
-      <c r="M2" s="94" t="s">
+      <c r="O2" s="16" t="s">
         <v>747</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>739</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -45989,7 +45978,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="33" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="96" t="s">
-        <v>713</v>
+        <v>774</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -46016,34 +46005,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="80" t="s">
+        <v>713</v>
+      </c>
+      <c r="E2" s="81" t="s">
         <v>714</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="F2" s="81" t="s">
         <v>715</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="G2" s="81" t="s">
         <v>716</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="H2" s="82" t="s">
         <v>717</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="I2" s="83" t="s">
         <v>718</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="J2" s="83" t="s">
         <v>719</v>
       </c>
-      <c r="J2" s="83" t="s">
+      <c r="K2" s="81" t="s">
         <v>720</v>
       </c>
-      <c r="K2" s="81" t="s">
+      <c r="L2" s="81" t="s">
         <v>721</v>
       </c>
-      <c r="L2" s="81" t="s">
+      <c r="M2" s="81" t="s">
         <v>722</v>
-      </c>
-      <c r="M2" s="81" t="s">
-        <v>723</v>
       </c>
       <c r="N2" s="84" t="s">
         <v>258</v>

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF558CF2-22C7-C644-BF37-9285823665BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46525C24-A1D3-F24E-95B3-6B7855813156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="1080" windowWidth="30240" windowHeight="17480" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5685,198 +5685,6 @@
     <t>Alert Message</t>
   </si>
   <si>
-    <r>
-      <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-All fields are mandatory for each VCN except "DNS Label" and "Defined Tag".
-Tags apply to the VCNs only and not to its components like IGW,NGW,SGW,DRG,LPG.
-"VCN name"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -  VCN names should be unique and are case-sensitie across sheets.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"CIDR Blocks" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- Enter comma seperated CIDRs to have multiple CIDR blocks attached to VCN.
-"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DNS Label"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -  Default value is "VCN Name" truncated to 15 chars (when left empty).If specified as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'n'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, DNS will not be enabled for the VCN.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Valid Values for columns E,F,G,H - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>y|n|&lt;component_name&gt; i.e. specify 'n' when a component(like IGW) is 
-                                                                    not required to be configured(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PHXHub-VCN in sample data), 
-                                                                 - specify name of the component- component will be configured with the
-                                                                    mentioned name(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PHX-DRG for the DRG in PHXHub-VCN) ,
-                                                                 - specify 'y' if component needs to be configured with default name i.e. 
-                                                                    &lt;vcnname&gt;_ngw(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PHXNonProd-VCN_ngw)
-                                                    </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Route Table associated with DRG/IGW/NGW/SGW can be specified in below format:
-                                                    y::&lt;Route Table Name&gt; or &lt;component_name::&lt;Route Table Name&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Autotune Type</t>
   </si>
   <si>
@@ -11137,51 +10945,6 @@
     <t>Singapore-2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2025.2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Updated ADB sheet, VCNs sheet</t>
-    </r>
-  </si>
-  <si>
     <t>Oracle GUA IPv6 Enabled</t>
   </si>
   <si>
@@ -11435,6 +11198,243 @@
   </si>
   <si>
     <t>Data Storage Size</t>
+  </si>
+  <si>
+    <r>
+      <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+All fields are mandatory for each VCN except "DNS Label" and "Defined Tag".
+Tags apply to the VCNs only and not to its components like IGW,NGW,SGW,DRG,LPG.
+"VCN name"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  VCN names should be unique and are case-sensitie across sheets.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"CIDR Blocks" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Enter comma seperated CIDRs to have multiple CIDR blocks attached to VCN.
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DNS Label"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  Default value is "VCN Name" truncated to 15 chars (when left empty).If specified as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'n'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, DNS will not be enabled for the VCN.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Valid Values for columns H, I, J, K, L - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y|n|&lt;component_name&gt; i.e. specify 'n' when a component(like IGW) is 
+                                                                    not required to be configured(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PHXHub-VCN in sample data), 
+                                                                 - specify name of the component- component will be configured with the
+                                                                    mentioned name(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PHX-DRG for the DRG in PHXHub-VCN) ,
+                                                                 - specify 'y' if component needs to be configured with default name i.e. 
+                                                                    &lt;vcnname&gt;_ngw(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PHXNonProd-VCN_ngw)
+                                                    </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Route Table associated with DRG/IGW/NGW/SGW can be specified in below format:
+                                                    y::&lt;Route Table Name&gt; or &lt;component_name::&lt;Route Table Name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2025.2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Updated ADB sheet, VCNs sheet, Groups and Policies as per CIS LZ</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -17598,7 +17598,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -17633,7 +17633,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="247" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>693</v>
+        <v>805</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -17644,7 +17644,7 @@
       <c r="H1" s="104"/>
       <c r="I1" s="105"/>
       <c r="J1" s="103" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="K1" s="104"/>
       <c r="L1" s="104"/>
@@ -17666,13 +17666,13 @@
         <v>484</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>797</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>798</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>799</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -17738,7 +17738,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -17812,7 +17812,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="30" customFormat="1" ht="94" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B1" s="108"/>
     </row>
@@ -17878,7 +17878,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -18006,7 +18006,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>29</v>
@@ -23883,7 +23883,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="226" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B1" s="115"/>
       <c r="C1" s="115"/>
@@ -23893,7 +23893,7 @@
       <c r="G1" s="115"/>
       <c r="H1" s="116"/>
       <c r="I1" s="103" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J1" s="104"/>
       <c r="K1" s="104"/>
@@ -23926,7 +23926,7 @@
         <v>67</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G2" s="24" t="s">
         <v>69</v>
@@ -24016,7 +24016,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -24068,16 +24068,16 @@
         <v>258</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>693</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>694</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="M2" s="25" t="s">
         <v>695</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="N2" s="25" t="s">
         <v>696</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>697</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>495</v>
@@ -24141,7 +24141,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="169" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -24155,7 +24155,7 @@
       <c r="K1" s="104"/>
       <c r="L1" s="105"/>
       <c r="M1" s="117" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="N1" s="118"/>
       <c r="O1" s="118"/>
@@ -24178,58 +24178,58 @@
         <v>65</v>
       </c>
       <c r="D2" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>716</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>737</v>
-      </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="25" t="s">
         <v>717</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>718</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="J2" s="25" t="s">
         <v>719</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="K2" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="L2" s="25" t="s">
         <v>721</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>722</v>
       </c>
       <c r="M2" s="25" t="s">
         <v>84</v>
       </c>
       <c r="N2" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="O2" s="25" t="s">
         <v>723</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="P2" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="Q2" s="25" t="s">
         <v>725</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="R2" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="T2" s="25" t="s">
         <v>728</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="U2" s="25" t="s">
         <v>729</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>730</v>
       </c>
       <c r="V2" s="25" t="s">
         <v>255</v>
@@ -24299,7 +24299,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -24316,7 +24316,7 @@
       <c r="N1" s="104"/>
       <c r="O1" s="105"/>
       <c r="P1" s="114" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="Q1" s="115"/>
       <c r="R1" s="115"/>
@@ -24361,10 +24361,10 @@
         <v>516</v>
       </c>
       <c r="H2" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>740</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>741</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>517</v>
@@ -24379,7 +24379,7 @@
         <v>520</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>521</v>
@@ -24403,7 +24403,7 @@
         <v>523</v>
       </c>
       <c r="V2" s="25" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="W2" s="25" t="s">
         <v>65</v>
@@ -24418,7 +24418,7 @@
         <v>525</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AB2" s="25" t="s">
         <v>526</v>
@@ -24488,7 +24488,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -24529,7 +24529,7 @@
         <v>386</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>88</v>
@@ -24608,7 +24608,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="121" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -24652,7 +24652,7 @@
         <v>97</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>98</v>
@@ -24737,7 +24737,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -24967,7 +24967,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="30" customFormat="1" ht="173" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="100" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -24987,13 +24987,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F2" s="72" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G2" s="72" t="s">
         <v>255</v>
@@ -25784,7 +25784,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="110" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -25798,7 +25798,7 @@
         <v>87</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>634</v>
@@ -25872,7 +25872,7 @@
         <v>500</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>501</v>
@@ -26259,10 +26259,10 @@
         <v>505</v>
       </c>
       <c r="G2" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>698</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>699</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>100</v>
@@ -26274,7 +26274,7 @@
         <v>266</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -26314,7 +26314,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -26347,10 +26347,10 @@
         <v>507</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>508</v>
@@ -26365,16 +26365,16 @@
         <v>205</v>
       </c>
       <c r="J2" s="15" t="s">
+        <v>801</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>803</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>804</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>805</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>806</v>
       </c>
       <c r="N2" s="15" t="s">
         <v>509</v>
@@ -26463,7 +26463,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -26503,7 +26503,7 @@
         <v>65</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E2" s="89" t="s">
         <v>448</v>
@@ -32427,7 +32427,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B1" s="115"/>
       <c r="C1" s="115"/>
@@ -32467,10 +32467,10 @@
         <v>471</v>
       </c>
       <c r="E2" s="38" t="s">
+        <v>751</v>
+      </c>
+      <c r="F2" s="38" t="s">
         <v>752</v>
-      </c>
-      <c r="F2" s="38" t="s">
-        <v>753</v>
       </c>
       <c r="G2" s="38" t="s">
         <v>450</v>
@@ -36761,7 +36761,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="138" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="122" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B1" s="123"/>
       <c r="C1" s="123"/>
@@ -36891,7 +36891,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B1" s="123"/>
       <c r="C1" s="123"/>
@@ -36915,7 +36915,7 @@
         <v>641</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>652</v>
@@ -36995,7 +36995,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="30" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -37013,19 +37013,19 @@
         <v>594</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>760</v>
-      </c>
       <c r="G2" s="93" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>255</v>
@@ -38121,7 +38121,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -38130,7 +38130,7 @@
       <c r="F1" s="99"/>
       <c r="G1" s="99"/>
       <c r="H1" s="106" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I1" s="120"/>
       <c r="J1" s="120"/>
@@ -38145,46 +38145,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="C2" s="85" t="s">
         <v>700</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="D2" s="15" t="s">
         <v>701</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>702</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>706</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="J2" s="86" t="s">
+        <v>708</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="M2" s="87" t="s">
+        <v>711</v>
+      </c>
+      <c r="N2" s="15" t="s">
         <v>703</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>705</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>706</v>
-      </c>
-      <c r="H2" s="60" t="s">
-        <v>707</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>708</v>
-      </c>
-      <c r="J2" s="86" t="s">
-        <v>709</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>710</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>711</v>
-      </c>
-      <c r="M2" s="87" t="s">
+      <c r="O2" s="15" t="s">
         <v>712</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>704</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -39325,7 +39325,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="128" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1" s="123"/>
       <c r="C1" s="123"/>
@@ -39335,7 +39335,7 @@
       <c r="G1" s="123"/>
       <c r="H1" s="124"/>
       <c r="I1" s="114" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="J1" s="115"/>
       <c r="K1" s="115"/>
@@ -39372,10 +39372,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="96" t="s">
+        <v>771</v>
+      </c>
+      <c r="F2" s="95" t="s">
         <v>772</v>
-      </c>
-      <c r="F2" s="95" t="s">
-        <v>773</v>
       </c>
       <c r="G2" s="96" t="s">
         <v>65</v>
@@ -39384,64 +39384,64 @@
         <v>67</v>
       </c>
       <c r="I2" s="96" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J2" s="95" t="s">
         <v>66</v>
       </c>
       <c r="K2" s="95" t="s">
+        <v>773</v>
+      </c>
+      <c r="L2" s="95" t="s">
         <v>774</v>
-      </c>
-      <c r="L2" s="95" t="s">
-        <v>775</v>
       </c>
       <c r="M2" s="96" t="s">
         <v>70</v>
       </c>
       <c r="N2" s="96" t="s">
+        <v>775</v>
+      </c>
+      <c r="O2" s="96" t="s">
         <v>776</v>
       </c>
-      <c r="O2" s="96" t="s">
+      <c r="P2" s="96" t="s">
         <v>777</v>
       </c>
-      <c r="P2" s="96" t="s">
+      <c r="Q2" s="96" t="s">
         <v>778</v>
       </c>
-      <c r="Q2" s="96" t="s">
+      <c r="R2" s="96" t="s">
         <v>779</v>
       </c>
-      <c r="R2" s="96" t="s">
+      <c r="S2" s="96" t="s">
         <v>780</v>
       </c>
-      <c r="S2" s="96" t="s">
+      <c r="T2" s="96" t="s">
         <v>781</v>
       </c>
-      <c r="T2" s="96" t="s">
+      <c r="U2" s="96" t="s">
         <v>782</v>
       </c>
-      <c r="U2" s="96" t="s">
+      <c r="V2" s="96" t="s">
         <v>783</v>
       </c>
-      <c r="V2" s="96" t="s">
+      <c r="W2" s="96" t="s">
         <v>784</v>
       </c>
-      <c r="W2" s="96" t="s">
+      <c r="X2" s="96" t="s">
         <v>785</v>
       </c>
-      <c r="X2" s="96" t="s">
+      <c r="Y2" s="96" t="s">
         <v>786</v>
       </c>
-      <c r="Y2" s="96" t="s">
+      <c r="Z2" s="96" t="s">
         <v>787</v>
-      </c>
-      <c r="Z2" s="96" t="s">
-        <v>788</v>
       </c>
       <c r="AA2" s="96" t="s">
         <v>61</v>
       </c>
       <c r="AB2" s="96" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AC2" s="95" t="s">
         <v>255</v>
@@ -45475,7 +45475,7 @@
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -45501,13 +45501,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="24" t="s">
+        <v>790</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>791</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="G2" s="24" t="s">
         <v>792</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>793</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>255</v>
@@ -48607,7 +48607,7 @@
       </c>
       <c r="F38" s="44"/>
       <c r="G38" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H38" s="44"/>
       <c r="I38" s="44"/>
@@ -48643,7 +48643,7 @@
     <row r="39" spans="1:35" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F39" s="44"/>
       <c r="G39" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H39" s="44"/>
       <c r="I39" s="44"/>
@@ -50339,7 +50339,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="30" customFormat="1" ht="131.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -51939,7 +51939,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="30" customFormat="1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -54431,7 +54431,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="30" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46525C24-A1D3-F24E-95B3-6B7855813156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF03529F-AC2A-D249-A459-1727BE39A712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="1080" windowWidth="30240" windowHeight="17480" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1080" windowWidth="28800" windowHeight="17480" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -10945,9 +10945,6 @@
     <t>Singapore-2</t>
   </si>
   <si>
-    <t>Oracle GUA IPv6 Enabled</t>
-  </si>
-  <si>
     <t>ULA IPv6 CIDR</t>
   </si>
   <si>
@@ -11435,6 +11432,9 @@
       <t xml:space="preserve">
 Updated ADB sheet, VCNs sheet, Groups and Policies as per CIS LZ</t>
     </r>
+  </si>
+  <si>
+    <t>Is Oracle GUA Allocation Enabled</t>
   </si>
 </sst>
 </file>
@@ -17598,7 +17598,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -17633,7 +17633,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="247" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="103" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
@@ -17666,13 +17666,13 @@
         <v>484</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>795</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>796</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>797</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -18006,7 +18006,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>29</v>
@@ -26314,7 +26314,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="99" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -26347,7 +26347,7 @@
         <v>507</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>736</v>
@@ -26365,16 +26365,16 @@
         <v>205</v>
       </c>
       <c r="J2" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="K2" s="15" t="s">
         <v>801</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>802</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>803</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>804</v>
       </c>
       <c r="N2" s="15" t="s">
         <v>509</v>

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF03529F-AC2A-D249-A459-1727BE39A712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0580AC1E-0FBA-6748-89D1-B8822C53DD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1080" windowWidth="28800" windowHeight="17480" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B0B012-7156-6549-9B5A-42C408225E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA357495-56B2-2F44-9949-7C24D9C27283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,7 +835,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="822">
   <si>
     <t>Region</t>
   </si>
@@ -11343,6 +11343,9 @@
       <t xml:space="preserve">
 Updated Instances sheet, Exa-Infra sheet</t>
     </r>
+  </si>
+  <si>
+    <t>Plugin OS Management Service Agent</t>
   </si>
 </sst>
 </file>
@@ -23760,7 +23763,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -23786,11 +23789,12 @@
     <col min="21" max="21" width="13.1640625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="12.83203125" hidden="1" customWidth="1"/>
     <col min="23" max="29" width="0" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="311" customHeight="1">
+    <row r="1" spans="1:37" ht="311" customHeight="1">
       <c r="A1" s="114" t="s">
         <v>767</v>
       </c>
@@ -23830,9 +23834,10 @@
       <c r="AG1" s="101"/>
       <c r="AH1" s="101"/>
       <c r="AI1" s="101"/>
-      <c r="AJ1" s="102"/>
-    </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="83.25" customHeight="1">
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="102"/>
+    </row>
+    <row r="2" spans="1:37" s="30" customFormat="1" ht="83.25" customHeight="1">
       <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
@@ -23918,34 +23923,37 @@
         <v>818</v>
       </c>
       <c r="AC2" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="AD2" s="25" t="s">
         <v>819</v>
       </c>
-      <c r="AD2" s="24" t="s">
+      <c r="AE2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="AE2" s="24" t="s">
+      <c r="AF2" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AG2" s="25" t="s">
         <v>373</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AH2" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="AH2" s="25" t="s">
+      <c r="AI2" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AJ2" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="AJ2" s="24" t="s">
+      <c r="AK2" s="24" t="s">
         <v>255</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:AJ1"/>
+    <mergeCell ref="I1:AK1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="D1:D1048576 H3:P1048576 S3:XFD1048576 E1:XFD2 A1:C2" xr:uid="{70506928-0DD3-F44D-BCEE-021DFE2CA7EA}"/>

--- a/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Blank-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA357495-56B2-2F44-9949-7C24D9C27283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F960A370-F1A3-1943-BB13-E08FDF781A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,7 +835,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="824">
   <si>
     <t>Region</t>
   </si>
@@ -11300,6 +11300,9 @@
     <t>Plugin Bastion</t>
   </si>
   <si>
+    <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -11341,11 +11344,14 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Updated Instances sheet, Exa-Infra sheet</t>
-    </r>
-  </si>
-  <si>
-    <t>Plugin OS Management Service Agent</t>
+Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
+    </r>
+  </si>
+  <si>
+    <t>Database Server Type</t>
+  </si>
+  <si>
+    <t>Storage Server Type</t>
   </si>
 </sst>
 </file>
@@ -11984,7 +11990,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -12302,6 +12308,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -17506,7 +17515,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="57" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
   </sheetData>
@@ -23923,7 +23932,7 @@
         <v>818</v>
       </c>
       <c r="AC2" s="25" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AD2" s="25" t="s">
         <v>819</v>
@@ -24694,21 +24703,23 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="9.83203125" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="9" width="12.5" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="10.1640625" customWidth="1"/>
     <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="126" customHeight="1">
+    <row r="1" spans="1:18" ht="120" customHeight="1">
       <c r="A1" s="99" t="s">
         <v>745</v>
       </c>
@@ -24728,8 +24739,9 @@
       <c r="O1" s="99"/>
       <c r="P1" s="99"/>
       <c r="Q1" s="99"/>
-    </row>
-    <row r="2" spans="1:17" ht="46.5" customHeight="1">
+      <c r="R1" s="99"/>
+    </row>
+    <row r="2" spans="1:18" ht="46.5" customHeight="1">
       <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
@@ -24743,48 +24755,51 @@
         <v>150</v>
       </c>
       <c r="E2" s="25" t="s">
+        <v>747</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="H2" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="I2" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="J2" s="25" t="s">
         <v>498</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="K2" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="L2" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="M2" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="M2" s="56" t="s">
+      <c r="N2" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="O2" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="P2" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="Q2" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="R2" s="25" t="s">
         <v>265</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:XFD1048576" xr:uid="{82B06929-4D5B-CD4D-9081-6B5E2F26AE97}"/>
@@ -29546,7 +29561,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H921"/>
+  <dimension ref="A1:J921"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -29557,7 +29572,7 @@
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="119.25" customHeight="1">
+    <row r="1" spans="1:10" ht="119.25" customHeight="1">
       <c r="A1" s="103" t="s">
         <v>640</v>
       </c>
@@ -29568,73 +29583,81 @@
       <c r="F1" s="104"/>
       <c r="G1" s="104"/>
       <c r="H1" s="104"/>
-    </row>
-    <row r="2" spans="1:8" ht="48">
-      <c r="A2" s="38" t="s">
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+    </row>
+    <row r="2" spans="1:10" ht="48">
+      <c r="A2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="39" t="s">
         <v>468</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="94" t="s">
         <v>469</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="94" t="s">
         <v>470</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="94" t="s">
+        <v>822</v>
+      </c>
+      <c r="I2" s="94" t="s">
+        <v>823</v>
+      </c>
+      <c r="J2" s="129" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="E3" s="53"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="E4" s="53"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="E5" s="53"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="E6" s="53"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="E7" s="53"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="E8" s="53"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="E9" s="53"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="E10" s="53"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="E11" s="53"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="E12" s="53"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="E14" s="53"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="E15" s="53"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="E16" s="53"/>
     </row>
     <row r="17" spans="5:5">
@@ -32354,7 +32377,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="A1:XFD1048576" xr:uid="{F9F57CFA-844D-914A-9912-7C8A550AEC75}"/>
